--- a/Ódor Artúr/érettségi/k_digkultfor_25okt_fl/szerencsepentek_25p.xlsx
+++ b/Ódor Artúr/érettségi/k_digkultfor_25okt_fl/szerencsepentek_25p.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c21c437aeb2245f/Dokumentumok/fakt2025/Ódor Artúr/érettségi/k_digkultfor_25okt_fl/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\europa04\Documents\fakt2025\Ódor Artúr\érettségi\k_digkultfor_25okt_fl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{35AC1C00-B90A-4F49-9541-51E69204B9E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{7335ED89-64C6-4D51-8932-9E4FEEDF020D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84688BF0-7EA7-4572-8E62-2A367A6CB19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" xr2:uid="{72C6F4CF-BD09-46E3-AC98-D417B4BA1D73}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{72C6F4CF-BD09-46E3-AC98-D417B4BA1D73}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,18 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -105,7 +117,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="General&quot; pont&quot;"/>
+    <numFmt numFmtId="164" formatCode="General&quot; pont&quot;"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -191,9 +203,15 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -202,12 +220,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -369,10 +381,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2</c:v>
@@ -390,22 +402,22 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -454,7 +466,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="t" anchorCtr="0"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="t" anchorCtr="0"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -1496,19 +1508,19 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="str">
+      <c r="B2" s="4" t="str">
         <f ca="1">CHOOSE(RANDBETWEEN(1,2),"i","f")</f>
-        <v>i</v>
-      </c>
-      <c r="C2" s="7" t="str">
+        <v>f</v>
+      </c>
+      <c r="C2" s="4" t="str">
         <f t="shared" ref="C2:E2" ca="1" si="0">CHOOSE(RANDBETWEEN(1,2),"i","f")</f>
-        <v>i</v>
-      </c>
-      <c r="D2" s="7" t="str">
+        <v>f</v>
+      </c>
+      <c r="D2" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>i</v>
       </c>
-      <c r="E2" s="7" t="str">
+      <c r="E2" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>i</v>
       </c>
@@ -1517,12 +1529,12 @@
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1543,30 +1555,30 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="5">
         <f ca="1">SUM(B20:E20)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3">
         <f ca="1">$B$1*F5</f>
-        <v>2000</v>
-      </c>
-      <c r="I5" s="8">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <f ca="1">COUNTIFS($F$5:$F$17,I5)</f>
         <v>1</v>
       </c>
@@ -1579,30 +1591,30 @@
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="D6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="5">
         <f t="shared" ref="F6:F17" ca="1" si="1">SUM(B21:E21)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" ref="G6:G17" ca="1" si="2">$B$1*F6</f>
-        <v>2000</v>
-      </c>
-      <c r="I6" s="8">
-        <v>1</v>
-      </c>
-      <c r="J6" s="8">
+        <v>4000</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
         <f t="shared" ref="J6:J9" ca="1" si="3">COUNTIFS($F$5:$F$17,I6)</f>
         <v>0</v>
       </c>
@@ -1615,19 +1627,19 @@
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="D7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
@@ -1635,16 +1647,16 @@
         <f t="shared" ca="1" si="2"/>
         <v>2000</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="5">
         <v>2</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="M7" t="s">
         <v>23</v>
@@ -1654,19 +1666,19 @@
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="8">
+      <c r="E8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
@@ -1674,10 +1686,10 @@
         <f t="shared" ca="1" si="2"/>
         <v>2000</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="5">
         <v>3</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>3</v>
       </c>
@@ -1693,19 +1705,19 @@
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="C9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="8">
+      <c r="E9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
@@ -1713,35 +1725,35 @@
         <f t="shared" ca="1" si="2"/>
         <v>2000</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="5">
         <v>4</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>4000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="8">
+      <c r="D10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>3</v>
       </c>
@@ -1757,19 +1769,19 @@
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="8">
+      <c r="C11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>3</v>
       </c>
@@ -1785,69 +1797,69 @@
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="8">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="8">
+      <c r="D13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="C14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="8">
+      <c r="E14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
@@ -1860,44 +1872,44 @@
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="8">
+      <c r="D15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="8">
+      <c r="D16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>3</v>
       </c>
@@ -1910,25 +1922,25 @@
       <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -1937,11 +1949,11 @@
       </c>
       <c r="B20">
         <f ca="1">IF(B$2=B5,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
         <f t="shared" ref="C20:E20" ca="1" si="5">IF(C$2=C5,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="5"/>
@@ -1958,11 +1970,11 @@
       </c>
       <c r="B21">
         <f t="shared" ref="B21:E32" ca="1" si="6">IF(B$2=B6,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="6"/>
@@ -1979,11 +1991,11 @@
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="6"/>
@@ -2000,11 +2012,11 @@
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="6"/>
@@ -2021,11 +2033,11 @@
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="6"/>
@@ -2042,11 +2054,11 @@
       </c>
       <c r="B25">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <f t="shared" ca="1" si="6"/>
@@ -2063,11 +2075,11 @@
       </c>
       <c r="B26">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="6"/>
@@ -2084,11 +2096,11 @@
       </c>
       <c r="B27">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="6"/>
@@ -2105,11 +2117,11 @@
       </c>
       <c r="B28">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="6"/>
@@ -2126,11 +2138,11 @@
       </c>
       <c r="B29">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <f t="shared" ca="1" si="6"/>
@@ -2147,11 +2159,11 @@
       </c>
       <c r="B30">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="6"/>
@@ -2168,11 +2180,11 @@
       </c>
       <c r="B31">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <f t="shared" ca="1" si="6"/>
@@ -2189,11 +2201,11 @@
       </c>
       <c r="B32">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <f t="shared" ca="1" si="6"/>
